--- a/samples/default_cell_style_output.xlsx
+++ b/samples/default_cell_style_output.xlsx
@@ -110,7 +110,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
